--- a/mvc/unidades_registro.xlsx
+++ b/mvc/unidades_registro.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,8 +30,12 @@
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +46,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF2C3E50"/>
         <bgColor rgb="FF2C3E50"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002C3E50"/>
+        <bgColor rgb="002C3E50"/>
       </patternFill>
     </fill>
   </fills>
@@ -72,9 +82,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -442,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -454,47 +467,47 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>FECHA</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>HORA</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>UNIDAD</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>KM</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>PO</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>TURNO</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>JURISDICCION</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>OBSERVACIONES</t>
         </is>
@@ -503,96 +516,116 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17:34:26</t>
+          <t>04:09:16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>🚙 4 EUI-646</t>
+          <t>🚙 1 EUI-621</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>NOCHE, DÍA, TARDE</t>
+          <t>NOCHE, DÍA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>T.ALTA</t>
+          <t>NORTE</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>FALTA 7 KM, COMPLETO, PO requerido</t>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>COMPLETO, COMPLETO, COMPLETO (3 P.O.)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>17:34:26</t>
+          <t>04:09:16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🚙 5 EUI-685</t>
+          <t>🚙 2 EUI-682</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>90</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>NOCHE, DÍA, TARDE</t>
+          <t>NOCHE, DÍA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>SECTORIAL</t>
+          <t>CENTRO</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>FALTA 26 KM, COMPLETO, PO requerido</t>
+          <t>CENTRO</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>COMPLETO, COMPLETO, COMPLETO (3 P.O.)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>17:34:26</t>
+          <t>04:09:16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -602,39 +635,49 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>NOCHE, DÍA, TARDE</t>
+          <t>TARDE</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>T.ALTA</t>
+          <t>SUR</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>FALTA 23 KM, COMPLETO, PO requerido</t>
+          <t>SUR</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>FALTA 45 KM, FALTA 50 MIN (2T), FALTAN 1 P.O.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17:34:26</t>
+          <t>04:09:16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -644,39 +687,49 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>50</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>NOCHE, DÍA, TARDE</t>
+          <t>NOCHE</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>SECTORIAL</t>
+          <t>ENACE</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>FALTA 30 KM, COMPLETO, PO requerido</t>
+          <t>ENACE</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>FALTA 40 KM, FALTA 130 MIN (5T), FALTAN 2 P.O.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>17:34:26</t>
+          <t>04:09:16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -686,12 +739,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>30</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -701,460 +759,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>T.ALTA</t>
+          <t>NORTE</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>FALTA 82 KM, FALTA 150 MIN (5T), PO requerido</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>17:34:26</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>🚘 11 EUI-668</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>TARDE</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>SECTORIAL</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>FALTA 78 KM, FALTA 170 MIN (6T), PO requerido</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>17:34:26</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>🚘 12 EUI-670</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>505</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>NOCHE, DÍA, TARDE</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>SECTORIAL</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>FALTA 13 KM, COMPLETO, PO requerido</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>06/09/2026</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>02:52:41</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>🚙 1 EUI-621</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>NOCHE, DÍA, TARDE</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>T.ALTA</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>ENACE</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>COMPLETO, FALTA 10 MIN (1T), COMPLETO (3 P.O.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>06/09/2026</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>02:52:41</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>🚙 2 EUI-682</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>NOCHE, DÍA</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>SECTORIAL</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>CENTRO</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>COMPLETO, COMPLETO, COMPLETO (3 P.O.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>06/09/2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>02:52:41</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>🚙 3 EUI-683</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>DÍA, TARDE</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>SECTORIAL</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
           <t>NORTE</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>FALTA 45 KM, FALTA 50 MIN (2T), FALTAN 1 P.O.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>06/09/2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>02:52:41</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>🚙 4 EUI-646</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>NOCHE</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>T.ALTA</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>ENACE</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>COMPLETO, FALTA 30 MIN (1T), FALTAN 2 P.O.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>06/09/2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>02:52:41</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>🚘 9 EUI-645</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>DÍA</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>T.ALTA</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>SUR</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>COMPLETO, COMPLETO, COMPLETO (3 P.O.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>06/09/2026</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>02:52:41</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>🚘 10 EUI-647</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>NOCHE, TARDE</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>SECTORIAL</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>CENTRO</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>COMPLETO (+80 KM), COMPLETO, COMPLETO (4 P.O.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>06/09/2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>02:52:41</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>🚘 11 EUI-668</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>NOCHE, TARDE</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>SECTORIAL</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>NORTE</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>FALTA 45 KM, FALTA 130 MIN (5T), FALTAN 1 P.O.</t>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>FALTA 60 KM, FALTA 80 MIN (3T), COMPLETO (3 P.O.)</t>
         </is>
       </c>
     </row>
